--- a/research/phase-4/deliveries/2026-07-16_phase-4-v6-final/Phase_4_Product_Country_Matrix_v6.xlsx
+++ b/research/phase-4/deliveries/2026-07-16_phase-4-v6-final/Phase_4_Product_Country_Matrix_v6.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Country Matrix" sheetId="1" r:id="R588153616e3447fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Country Matrix" sheetId="1" r:id="Reb3ca481878d4357"/>
   </x:sheets>
 </x:workbook>
 </file>
